--- a/output/pdf_financials_xlsx/GMR.xlsx
+++ b/output/pdf_financials_xlsx/GMR.xlsx
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>6.027317</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.027317</v>
       </c>
     </row>
     <row r="93">
@@ -2582,7 +2582,11 @@
           <t>Reserves (Notes 5)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>6.027317</v>
       </c>

--- a/output/pdf_financials_xlsx/GMR.xlsx
+++ b/output/pdf_financials_xlsx/GMR.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.030192</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002611</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.030192</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002611</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.053724</v>
+        <v>0.023532</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.105704</v>
+        <v>0.103093</v>
       </c>
     </row>
     <row r="49">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/GMR.xlsx
+++ b/output/pdf_financials_xlsx/GMR.xlsx
@@ -3070,7 +3070,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.145</v>
       </c>
